--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>97965</v>
+        <v>97971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>97971</v>
+        <v>97973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>97973</v>
+        <v>97974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>97974</v>
+        <v>97980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>97980</v>
+        <v>97984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>97986</v>
+        <v>97988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>97988</v>
+        <v>98001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>98003</v>
+        <v>98006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>98006</v>
+        <v>98016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>98017</v>
+        <v>98022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>98022</v>
+        <v>98024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>98024</v>
+        <v>98030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>98030</v>
+        <v>98042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>98042</v>
+        <v>98043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34067-2026 artfynd.xlsx
+++ b/artfynd/A 34067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136916090</v>
       </c>
       <c r="B2" t="n">
-        <v>98043</v>
+        <v>98046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
